--- a/TestData/testdata_user.xlsx
+++ b/TestData/testdata_user.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vidhy\project\HRManagementGuvi\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vidhy\GuviProject_09_03\HR_Management_Web_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F0BAF7-5542-4295-95A7-C169C15CCB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200157E6-B563-4A4D-92E1-9273B899D539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5C6BD932-5D68-4AF8-96A4-9A61496B2DE0}"/>
   </bookViews>
@@ -601,7 +601,7 @@
         <v>0.50866898148148143</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>8</v>
